--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4803-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4803-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{306CB311-786E-4E4F-8C00-48EEF61B90E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90A0DFE0-9830-46E1-9BBE-C518A075E56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{339D919D-081B-4F88-AE79-C1D266CA599C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{7E2D2E4A-E5A2-4AC3-AE7F-45EEBAA087DF}"/>
   </bookViews>
   <sheets>
     <sheet name="4803-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1451,27 +1451,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3A72CCD-CAFF-4C51-B49F-E06C48816AFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15646E97-DA96-4652-B460-42913C9D13AA}">
   <dimension ref="A1:X16"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="6.75" customWidth="1"/>
-    <col min="5" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.875" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="5.88671875" customWidth="1"/>
+    <col min="5" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1505,7 +1505,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1541,7 +1541,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1661,7 +1661,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2021</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2020</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2013</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35" t="s">
         <v>38</v>
       </c>
